--- a/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
@@ -716,7 +716,7 @@
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>▸ Antes de templar se comprueba el AIRE del obrador: 18-20 °C y menos del 60 % de humedad. Las tres curvas de cobertura de esta hoja sólo funcionan dentro de esa ventana.</t>
+          <t>▸ Antes de templar se comprueba el AIRE del obrador: 18-20 °C y 50-60 % de humedad. Las tres curvas de cobertura de esta hoja sólo funcionan dentro de esa ventana.</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
+          <t>Versión 2.1 · octubre 2026 · aichef.pro/kit-tareas-chocolateria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Comprobar la temperatura y la humedad del obrador ANTES de templar: objetivo 18-20 °C y menos del 60 % de humedad (por encima, la manteca no cristaliza y aparece bloom) — anota la lectura: ____ °C</t>
+          <t>Comprobar la temperatura y la humedad del obrador ANTES de templar: objetivo 18-20 °C y 50-60 % de humedad (por encima, la manteca no cristaliza y aparece bloom) — anota la lectura: ____ °C</t>
         </is>
       </c>
       <c r="C9" s="14" t="inlineStr">

--- a/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
+++ b/astro-site/public/dl/kit-tareas-chocolateria/02-partidas-produccion.xlsx
@@ -1838,7 +1838,7 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>Envolver en papel/aluminio y etiquetar con lote y fecha</t>
+          <t>Envolver en papel/aluminio y etiquetar: denominación, ingredientes con los alérgenos destacados, peso neto, lote y fecha de consumo preferente</t>
         </is>
       </c>
       <c r="C25" s="14" t="inlineStr">
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>Etiquetar cada lote con fecha de producción y consumo preferente según su familia (tabla al pie de la hoja)</t>
+          <t>Etiquetar cada lote con fecha de producción y consumo preferente según su familia (tabla al pie de la hoja); la ganache de nata fresca, con fecha de caducidad (art. 24 del Reglamento UE 1169/2011)</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="B33" s="9" t="inlineStr">
         <is>
-          <t>Almacenar el producto terminado a 15-18 °C y 50-60 % de humedad, en oscuridad y lejos de olores fuertes (el cacao los absorbe) — anota la lectura: ____ °C</t>
+          <t>Almacenar el producto terminado a 15-18 °C y 50-60 % de humedad, en oscuridad y lejos de olores fuertes (el cacao los absorbe); la ganache de nata fresca, en cámara a 0-4 °C — anota la lectura: ____ °C</t>
         </is>
       </c>
       <c r="C33" s="17" t="inlineStr">
